--- a/关键标准答案.xlsx
+++ b/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R8872e1206b4846d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R45ca24c4f8484c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R2be4c38811c14862"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re77611cc3a3f445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rd10cbbdf785e4c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Red4e433f7ce148c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R311d1263bc5c44f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R55b2df044b2e4c5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rf9ea61fea9fb4d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc9d419f8b2a94fde"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,7 +495,7 @@
         <x:v>v3.17.3+ge4da497</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>真实Helm返回值</x:v>
+        <x:v>Helm返回值</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" customHeight="1">
